--- a/SuppXLS/Scen_UC_FHEAT_MANHEAT_10_30.xlsx
+++ b/SuppXLS/Scen_UC_FHEAT_MANHEAT_10_30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B54852B-B2DB-41C4-ACB1-C40572F46A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86BF7C4-5EEE-407F-B138-1F5C17AA3C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
@@ -98,9 +98,6 @@
     <t>UC_COMPRD</t>
   </si>
   <si>
-    <t>HEAT</t>
-  </si>
-  <si>
     <t>MANHEAT</t>
   </si>
   <si>
@@ -111,6 +108,9 @@
   </si>
   <si>
     <t>Maximum use of ELC in Furnace</t>
+  </si>
+  <si>
+    <t>DMD</t>
   </si>
 </sst>
 </file>
@@ -694,16 +694,16 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G6" t="s">
         <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -727,21 +727,21 @@
         <v>15</v>
       </c>
       <c r="O6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
+      <c r="G7" t="s">
         <v>20</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -765,7 +765,7 @@
         <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
